--- a/data/trans_dic/IP16A03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,13</t>
+          <t>0,0; 17,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,76</t>
+          <t>0,0; 21,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,76</t>
+          <t>0,0; 24,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,19</t>
+          <t>0,0; 20,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,62</t>
+          <t>0,0; 16,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,93</t>
+          <t>0,0; 42,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,74</t>
+          <t>0,0; 41,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 14,12</t>
+          <t>1,52; 13,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 13,08</t>
+          <t>1,5; 13,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 20,83</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 20,6</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 19,8</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 11,75</t>
+          <t>2,77; 10,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,92</t>
+          <t>1,55; 8,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,35</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 12,44</t>
+          <t>3,68; 12,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,17</t>
+          <t>1,21; 9,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,44</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,9</t>
+          <t>1,4; 7,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,86</t>
+          <t>3,86; 10,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,94</t>
+          <t>1,91; 7,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,59</t>
+          <t>0,48; 3,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,99</t>
+          <t>1,29; 5,08</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,38</t>
+          <t>0,0; 18,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,99</t>
+          <t>0,0; 13,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,13</t>
+          <t>0,0; 13,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 18,3</t>
+          <t>2,06; 18,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,62</t>
+          <t>1,6; 13,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 26,95</t>
+          <t>4,59; 24,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 14,33</t>
+          <t>2,59; 14,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 9,96</t>
+          <t>1,72; 10,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 15,39</t>
+          <t>3,4; 15,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,78</t>
+          <t>2,94; 9,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 8,02</t>
+          <t>2,24; 7,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,36</t>
+          <t>0,55; 4,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,48</t>
+          <t>0,44; 4,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 11,43</t>
+          <t>4,67; 12,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,26</t>
+          <t>1,7; 7,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,31</t>
+          <t>2,48; 9,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,31</t>
+          <t>1,62; 6,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,52</t>
+          <t>4,45; 9,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,28</t>
+          <t>2,53; 6,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,68</t>
+          <t>1,95; 5,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,52</t>
+          <t>1,35; 4,09</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2587</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1656</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3768</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4841</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3803</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4195</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2830</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3759</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6519</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>644; 5878</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>602; 5330</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5098</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6366</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4831</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3740</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2475</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6237</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11068</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7239</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2236; 8656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1369; 7582</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3249</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6786</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3223; 11064</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1221; 9270</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5121</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1679; 8537</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6493; 17008</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3618; 13354</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>810; 6245</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3108; 12241</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3908</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4085</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3408</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4614</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4280</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4952</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3893</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2202</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>726; 6413</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>632; 5437</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1324; 7192</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1497; 8234</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1306; 7898</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1960; 9083</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2145</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6564</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6081</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>17740</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12634</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8590</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>8977</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3687; 12295</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3304; 11738</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>696; 5671</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>773; 7380</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>6684; 17556</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2685; 12296</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3055; 11275</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2957; 11929</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11935; 25054</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>7727; 19215</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4879; 14984</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>4848; 14734</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Estudios-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,09</t>
+          <t>0,0; 17,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,44</t>
+          <t>0,0; 21,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,23</t>
+          <t>0,0; 25,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,71</t>
+          <t>0,0; 20,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,17</t>
+          <t>0,0; 14,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,78</t>
+          <t>0,0; 47,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,61</t>
+          <t>0,0; 36,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,89</t>
+          <t>1,51; 13,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 13,3</t>
+          <t>1,5; 13,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,83</t>
+          <t>0,0; 22,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,6</t>
+          <t>0,0; 20,82</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,73</t>
+          <t>2,59; 10,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,59</t>
+          <t>1,56; 8,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,53; 6,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,62</t>
+          <t>3,34; 12,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,18</t>
+          <t>1,14; 9,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,11</t>
+          <t>1,47; 7,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 10,1</t>
+          <t>4,12; 10,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,06</t>
+          <t>1,92; 6,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,7</t>
+          <t>0,48; 3,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,08</t>
+          <t>1,23; 5,06</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,98</t>
+          <t>0,0; 17,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,6</t>
+          <t>0,0; 12,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,52</t>
+          <t>0,0; 14,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 18,18</t>
+          <t>2,07; 18,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,79</t>
+          <t>1,6; 13,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 24,91</t>
+          <t>6,1; 26,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 14,24</t>
+          <t>2,68; 14,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,41</t>
+          <t>1,73; 9,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 15,75</t>
+          <t>3,36; 15,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,81</t>
+          <t>3,23; 9,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,97</t>
+          <t>2,36; 7,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,45</t>
+          <t>0,54; 4,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,15</t>
+          <t>0,46; 4,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,26</t>
+          <t>4,32; 11,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,78</t>
+          <t>1,85; 7,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,15</t>
+          <t>2,6; 9,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,55</t>
+          <t>1,64; 6,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,33</t>
+          <t>4,45; 9,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,3</t>
+          <t>2,38; 6,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,98</t>
+          <t>1,89; 5,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,09</t>
+          <t>1,32; 4,36</t>
         </is>
       </c>
     </row>
@@ -1504,17 +1504,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3768</t>
+          <t>0; 3800</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4841</t>
+          <t>0; 4768</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3803</t>
+          <t>0; 3971</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1524,42 +1524,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4195</t>
+          <t>0; 4117</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2830</t>
+          <t>0; 2623</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3759</t>
+          <t>0; 4149</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6519</t>
+          <t>0; 5756</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>644; 5878</t>
+          <t>637; 5777</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>602; 5330</t>
+          <t>601; 5238</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5098</t>
+          <t>0; 5508</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 6366</t>
+          <t>0; 6431</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2236; 8656</t>
+          <t>2089; 8860</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1369; 7582</t>
+          <t>1373; 7697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3249</t>
+          <t>0; 3412</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6786</t>
+          <t>640; 7572</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3223; 11064</t>
+          <t>2926; 10917</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1221; 9270</t>
+          <t>1150; 9240</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5121</t>
+          <t>0; 4750</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1679; 8537</t>
+          <t>1758; 8604</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6493; 17008</t>
+          <t>6939; 17170</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3618; 13354</t>
+          <t>3627; 12675</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>810; 6245</t>
+          <t>802; 6171</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3108; 12241</t>
+          <t>2960; 12177</t>
         </is>
       </c>
     </row>
@@ -1920,37 +1920,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4280</t>
+          <t>0; 4002</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4952</t>
+          <t>0; 4557</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3893</t>
+          <t>0; 4166</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2202</t>
+          <t>0; 1918</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>726; 6413</t>
+          <t>730; 6659</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>632; 5437</t>
+          <t>631; 5378</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1324; 7192</t>
+          <t>1762; 7689</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1960,22 +1960,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1497; 8234</t>
+          <t>1548; 8221</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1306; 7898</t>
+          <t>1308; 7023</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1960; 9083</t>
+          <t>1935; 8774</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2145</t>
+          <t>0; 2137</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3687; 12295</t>
+          <t>4042; 12371</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3304; 11738</t>
+          <t>3480; 11430</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>696; 5671</t>
+          <t>693; 5733</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>773; 7380</t>
+          <t>818; 7824</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6684; 17556</t>
+          <t>6185; 17006</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2685; 12296</t>
+          <t>2916; 11872</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3055; 11275</t>
+          <t>3205; 11629</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2957; 11929</t>
+          <t>2987; 11528</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11935; 25054</t>
+          <t>11943; 25313</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7727; 19215</t>
+          <t>7275; 19237</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4879; 14984</t>
+          <t>4736; 14087</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4848; 14734</t>
+          <t>4735; 15681</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,65%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,88%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6,12%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,24</t>
+          <t>0,0; 20,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,11</t>
+          <t>0,0; 16,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,3</t>
+          <t>0,0; 39,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 30,27</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 20,13</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 18,76</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 26,76</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 20,32</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,99</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 47,22</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 36,74</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,66</t>
+          <t>1,49; 14,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 13,07</t>
+          <t>1,5; 13,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,5</t>
+          <t>0,0; 20,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,82</t>
+          <t>0,0; 20,71</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,99%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,24%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 10,98</t>
+          <t>3,54; 12,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 8,72</t>
+          <t>0,87; 8,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,11</t>
+          <t>0,0; 6,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,27</t>
+          <t>1,44; 7,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 12,45</t>
+          <t>2,94; 11,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,15</t>
+          <t>1,61; 8,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,17</t>
+          <t>0,7; 6,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 10,2</t>
+          <t>4,12; 9,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,7</t>
+          <t>1,72; 6,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,66</t>
+          <t>0,35; 3,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,06</t>
+          <t>1,47; 5,92</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,32%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,97%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,54%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,75</t>
+          <t>2,05; 18,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,52</t>
+          <t>1,6; 13,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,47</t>
+          <t>4,69; 26,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 18,88</t>
+          <t>0,0; 17,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,64</t>
+          <t>0,0; 11,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,1; 26,63</t>
+          <t>0,0; 12,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 14,22</t>
+          <t>3,21; 14,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 9,26</t>
+          <t>1,72; 9,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 15,22</t>
+          <t>3,47; 15,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,46%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,87</t>
+          <t>4,11; 11,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,76</t>
+          <t>1,67; 7,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,5</t>
+          <t>2,51; 9,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,4</t>
+          <t>1,48; 6,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 11,88</t>
+          <t>3,11; 9,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,52</t>
+          <t>2,27; 8,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,43</t>
+          <t>0,55; 4,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,33</t>
+          <t>0,53; 4,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,43</t>
+          <t>4,58; 9,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,3</t>
+          <t>2,62; 6,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,62</t>
+          <t>1,74; 5,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,36</t>
+          <t>1,4; 4,55</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1373,37 +1373,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,44 +1436,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1245</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1379</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>765</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1343</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2587</t>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1289</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3800</t>
+          <t>0; 4089</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4768</t>
+          <t>0; 2908</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3971</t>
+          <t>0; 3508</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 4213</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4439</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4237</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4198</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4117</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2623</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4149</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5756</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>637; 5777</t>
+          <t>628; 5974</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>601; 5238</t>
+          <t>599; 5241</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5508</t>
+          <t>0; 5043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 6431</t>
+          <t>0; 4909</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6237</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3880</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4831</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3740</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>910</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2475</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6237</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3499</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6106</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2089; 8860</t>
+          <t>3102; 10908</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1373; 7697</t>
+          <t>881; 8255</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3412</t>
+          <t>0; 5517</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>640; 7572</t>
+          <t>1558; 8164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2926; 10917</t>
+          <t>2373; 9484</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1150; 9240</t>
+          <t>1417; 7868</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4750</t>
+          <t>0; 2876</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1758; 8604</t>
+          <t>645; 6247</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6939; 17170</t>
+          <t>6936; 16594</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3627; 12675</t>
+          <t>3249; 13140</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>802; 6171</t>
+          <t>585; 6054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2960; 12177</t>
+          <t>2939; 11877</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3908</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1445</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3908</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>366</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>366</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>724; 6452</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4557</t>
+          <t>630; 5372</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4166</t>
+          <t>1354; 7780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1918</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>730; 6659</t>
+          <t>0; 3919</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>631; 5378</t>
+          <t>0; 4366</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1762; 7689</t>
+          <t>0; 3493</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1572</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1548; 8221</t>
+          <t>1856; 8285</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1308; 7023</t>
+          <t>1301; 7555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1935; 8774</t>
+          <t>2003; 8873</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2137</t>
+          <t>0; 2299</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6564</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2380</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>7761</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4042; 12371</t>
+          <t>5892; 16367</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3480; 11430</t>
+          <t>2640; 11462</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>693; 5733</t>
+          <t>3098; 11480</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>818; 7824</t>
+          <t>2440; 10178</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6185; 17006</t>
+          <t>3898; 12252</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2916; 11872</t>
+          <t>3342; 11801</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3205; 11629</t>
+          <t>706; 5554</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2987; 11528</t>
+          <t>763; 6885</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11943; 25313</t>
+          <t>12294; 25555</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7275; 19237</t>
+          <t>8004; 19176</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4736; 14087</t>
+          <t>4362; 14236</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4735; 15681</t>
+          <t>4306; 14012</t>
         </is>
       </c>
     </row>
